--- a/Result/checksun_type/輸出入模組_介面卡.xlsx
+++ b/Result/checksun_type/輸出入模組_介面卡.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>217717</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>149413</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>216732</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>221658</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>301588</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>199194</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>216632</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>357016</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>609988</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>600689</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>797538</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>321219</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>681031</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>59.1</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>66.33</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>66.33</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>12083.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>5865.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>5865.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>7007.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>10890.04</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>10890.04</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-445.5266959299497</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>12083</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>12083.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>58.64</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>60.75</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>4249.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>4482.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>4482</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>6251.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>11196.28</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>11196.28</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1032.55162969036</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>4249</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>4249.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>58.48</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>61.12</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>66.94</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>66.94</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2446.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>6726.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>6726.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>6742.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>11603.32</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>11603.32</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-994.9246911448618</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2446</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2446.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>58.72000000000001</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>61.49</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>61.49</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>67.3</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>4543.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>7728.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>7728.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>8156.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>11950.58</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>11950.58</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-712.4603256818336</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>4543</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>4543.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>59.04</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>61.86</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>67.69</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>67.69</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>6007.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>8492.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>8492.200000000001</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>8361.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>12703.24</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>12703.24</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-508.1733633888707</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>6007</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>6007.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>59.23999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>62.21</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>67.99</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>67.98999999999999</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>5165.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>8148.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>8148.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>8022.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>13286.08</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>13286.08</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-355.0429399921777</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>5165</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>5165.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>59.86</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>62.73</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>62.73</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>68.33</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>15470.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>8021.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>8021.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>8870.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>14144.64</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>14144.64</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-33.39080156861201</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>15470</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>15470.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>60.48</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>63.2</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>68.71</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>68.70999999999999</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>7459.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>6759.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>6759.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>8777.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>14707.14</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>14707.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-676.8023609074944</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>7459</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>7459.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>60.58</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>63.55</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>69.09</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>63.55</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>69.09</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>8360.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>8583.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>8583.799999999999</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>9158.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>15482.56</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>15482.56</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-713.4687899306327</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>8360</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>8360.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>63.94</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>69.49</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>69.48999999999999</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>4288.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>8230.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>8230.799999999999</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>9635.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>19668.2</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>19668.2</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-836.9040888947329</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>4288</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>4288.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>60.98</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>64.26</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>70.02</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>70.02</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>4531.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>7895.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>7895.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>10371.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>20723.16</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>20723.16</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-547.0650842400664</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>4531</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>4531.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>18.99</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>22.56</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>513.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>481.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>481.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>955.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>945.86</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>945.86</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-112.0936968119468</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>513</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>513.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>18.96</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>20.84</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>22.66</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>22.66</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>686.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>652.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>652.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>1027.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>962.3</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>962.3</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-102.1091227620544</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>686</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>686.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>19.05</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>22.76</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>22.76</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>278.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>766.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>766.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>1078.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>965.32</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>965.3200000000001</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-102.7344054492778</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>278</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>278.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>19.18</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>21.28</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>22.86</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>457.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>999.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>999.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>1199.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>989.86</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>989.86</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-56.24429480783692</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>457</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>457.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>19.53</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>22.97</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>22.97</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>474.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1017.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1017</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1218.1</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1011.94</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1011.94</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-6.999697648355777</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>474</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>474.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>19.93</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>23.08</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>23.08</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1367.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1429.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1429.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1250.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1013.74</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1013.74</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>61.77828749548712</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1367</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1367.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>20.33</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>22.03</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>23.2</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1256.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>1402.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>1402.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1286.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1006.36</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1006.36</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>62.14761314756674</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1256</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1256.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>20.61</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>22.24</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>23.29</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>23.29</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>1444.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1391.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1391.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1259.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>991.4</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>991.4</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>72.3485207524102</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>1444</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>1444.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>20.86</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>22.44</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>23.38</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>544.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1399.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1399</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1179.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>984.14</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>984.14</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>64.1945130181723</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>544</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>544.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>21.06</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>23.46</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>23.46</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>2536.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1419.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1419.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1185.4</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>984.76</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>984.76</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>146.6818407900403</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>2536</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>2536.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>21.2</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>22.77</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>23.52</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>23.52</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>1231.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1071.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1071</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1030.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>962.14</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>962.14</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>45.85367186449298</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>1231</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>1231.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>104.4</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>106.52</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>111.25</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>106.52</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>111.25</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>777509323.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>2934553867.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>2934553867.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>2158280166.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>1031583879.48</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>1031583879.48</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>292289650.0664442</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>777509323</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>777509323.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>103.1</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>106.72</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>111.58</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>106.72</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>111.58</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1668288090.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>3096742737.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>3096742737</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>2135464180.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>1032124146.48</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>1032124146.48</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>494196663.578167</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1668288090</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1668288090.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>102.2</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>106.75</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>111.97</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>111.97</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>8321088018.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>3093155396.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>3093155396.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>2053773215.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>1018612141.58</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>1018612141.58</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>669544791.2885513</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>8321088018</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>8321088018.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>102.2</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>107.08</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>112.51</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>107.08</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>112.51</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>2053070263.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1728650118.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1728650118.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>1347672905.7</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>859682136.04</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>859682136.04</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>183329810.3287945</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>2053070263</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>2053070263.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>103.1</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>107.42</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>113.07</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>107.42</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>113.07</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1852813645.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1591834282.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1591834282.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1344225255.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>824134046.86</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>824134046.86</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>153762818.0531137</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1852813645</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1852813645.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>104.4</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>107.78</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>113.6</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>107.78</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>113.6</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1588453669.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1382006465.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1382006465.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1235144843.6</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>792783654.98</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>792783654.98</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>127488794.657387</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1588453669</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1588453669.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>106.1</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>108.18</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>114.16</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>108.18</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>114.16</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>1650351387.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>1174185623.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>1174185623</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>1167188797.5</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>769923303.52</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>769923303.52</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>113725587.4257281</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>1650351387</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>1650351387.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>107.3</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>108.48</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>114.65</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>108.48</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>114.65</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>1498561628.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>1014391034.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>1014391034</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>1102417113.0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>744968122.94</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>744968122.9400001</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>83370336.32958221</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>1498561628</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>1498561628.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>109.2</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>108.75</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>115.15</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>115.15</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>1368991084.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>966695693.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>966695693</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>1018447736.5</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>725784218.34</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>725784218.34</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>53291368.35903144</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>1368991084</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1368991084.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>110.8</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>108.95</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>115.58</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>115.58</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>803674560.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1096616229.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1096616229</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>944803139.0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>721693719.98</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>721693719.98</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>22300709.24542224</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>803674560</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>803674560.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>110.2</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>108.92</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>116.09</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>108.92</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>116.09</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>549349456.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1088283221.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1088283221.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>956600754.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>713664137.72</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>713664137.72</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>37801512.75292969</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>549349456</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>549349456.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>586.6</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>636.0</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>667.3</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>636</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>667.3</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>2251806679.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>2845492684.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>2845492684.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>3254023064.0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>2250939639.92</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>2250939639.92</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>80988449.20909452</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>2251806679</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>2251806679.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>577.4</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>640.85</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>668.88</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>640.85</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>668.88</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>2303990317.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>2895931468.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>2895931468.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>3423927956.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>2313304958.2</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>2313304958.2</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>168000892.6023631</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>2303990317</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>2303990317.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>572.0</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>646.8</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>670.44</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>670.4400000000001</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>4282414081.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>3701315712.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>3701315712</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>3406103963.5</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>2315429027.54</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>2315429027.54</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>280713247.2140913</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>4282414081</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>4282414081.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>653.25</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>671.96</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>671.96</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>3277325446.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>3639148367.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>3639148367.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>3149911827.2</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>2279747515.3</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>2279747515.3</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>219731448.8303423</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>3277325446</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>3277325446.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>589.0</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>659.5</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>673.4</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>673.4</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>2111926901.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>3434438489.8</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>3434438489.8</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>3061336173.2</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>2234436035.54</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>2234436035.54</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>232455110.2881894</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>2111926901</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>601.0</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>674.84</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>2504000596.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>3662553443.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>3053660242.7</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>2215412102.28</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>367193931.1105347</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>2504000596</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>2504000596.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>617.2</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>672.05</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>676.22</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>672.05</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>676.22</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>6330911536.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>3951924444.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>3951924444.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>3034497195.4</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>2193079344.64</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>2193079344.64</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>504555995.9956522</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>6330911536</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>6330911536.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>636.8</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>678.2</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>677.46</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>678.2</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>677.46</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>3971577357.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>3110892215.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>3110892215</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>2577610128.3</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>2089597881.18</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>2089597881.18</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>272741488.1174035</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>3971577357</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>3971577357.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>647.4</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>681.95</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>677.64</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>681.95</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>677.64</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>2253776059.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>2660675287.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>2660675287.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>2395309044.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>2031062259.28</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>2031062259.28</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>184622942.8942842</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>2253776059</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>2253776059.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>653.6</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>684.55</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>677.36</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>684.55</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>677.36</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>3252501668.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>2688233856.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>2688233856.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>2353124375.3</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>2012331643.46</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>2012331643.46</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>236195769.4007463</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>3252501668</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>3252501668.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>663.2</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>687.1</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>677.34</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>687.1</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>677.34</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>3950855603.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>2444767042.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>2444767042.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>2195634921.6</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1973519631.2</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1973519631.2</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>194429357.3956661</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>3950855603</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>3950855603.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
